--- a/data/trans_camb/POLIPATOLOGIA_2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_2-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,69</t>
+          <t>-1,23; 2,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,61</t>
+          <t>-0,83; 3,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 15,88</t>
+          <t>4,16; 16,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 5,91</t>
+          <t>-1,35; 5,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 5,7</t>
+          <t>-2,02; 5,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 18,57</t>
+          <t>5,98; 18,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,35</t>
+          <t>-0,67; 3,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,76</t>
+          <t>-0,53; 3,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 15,18</t>
+          <t>5,93; 14,52</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,2; 170,27</t>
+          <t>-40,68; 217,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 233,45</t>
+          <t>-27,77; 266,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125,81; 1063,48</t>
+          <t>116,97; 1006,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 94,87</t>
+          <t>-15,13; 91,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 94,17</t>
+          <t>-21,69; 87,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,16; 289,69</t>
+          <t>63,67; 299,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 78,59</t>
+          <t>-13,08; 85,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 96,35</t>
+          <t>-9,79; 90,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>106,2; 342,89</t>
+          <t>101,88; 342,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 5,19</t>
+          <t>0,32; 5,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,39</t>
+          <t>-0,87; 3,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 11,25</t>
+          <t>3,39; 11,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 0,98</t>
+          <t>-7,07; 0,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 0,87</t>
+          <t>-6,83; 1,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 45,41</t>
+          <t>6,77; 44,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,97</t>
+          <t>-2,47; 2,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,26</t>
+          <t>-2,28; 2,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 32,32</t>
+          <t>7,22; 32,9</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 156,95</t>
+          <t>2,48; 159,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 129,69</t>
+          <t>-17,13; 120,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,47; 330,98</t>
+          <t>60,49; 331,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,19; 7,49</t>
+          <t>-42,19; 6,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,68; 7,36</t>
+          <t>-40,53; 9,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,22; 353,16</t>
+          <t>43,24; 349,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 23,41</t>
+          <t>-23,58; 24,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 26,88</t>
+          <t>-22,84; 31,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,06; 378,27</t>
+          <t>75,25; 391,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,78</t>
+          <t>-2,82; 4,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 3,06</t>
+          <t>-3,75; 3,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 9,35</t>
+          <t>1,22; 8,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 9,36</t>
+          <t>0,22; 9,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 1,97</t>
+          <t>-6,35; 1,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 12,36</t>
+          <t>-0,63; 11,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 5,4</t>
+          <t>-0,26; 5,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,22</t>
+          <t>-4,21; 1,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 9,28</t>
+          <t>2,73; 9,26</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 45,91</t>
+          <t>-26,31; 53,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 41,95</t>
+          <t>-32,8; 40,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,65; 119,21</t>
+          <t>10,84; 111,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 57,78</t>
+          <t>0,29; 54,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,41; 12,06</t>
+          <t>-30,11; 10,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,49; 73,92</t>
+          <t>-0,29; 67,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 41,87</t>
+          <t>-2,13; 43,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 9,82</t>
+          <t>-26,7; 8,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,14; 70,43</t>
+          <t>17,8; 71,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 5,32</t>
+          <t>-3,96; 5,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 10,85</t>
+          <t>1,31; 10,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 16,28</t>
+          <t>-7,7; 16,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 9,77</t>
+          <t>-1,58; 9,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 8,32</t>
+          <t>-2,47; 8,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,95; 18,0</t>
+          <t>4,37; 17,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 6,42</t>
+          <t>-1,28; 6,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,85</t>
+          <t>0,45; 7,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 15,07</t>
+          <t>-3,87; 15,43</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 39,34</t>
+          <t>-22,53; 40,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,12; 81,49</t>
+          <t>7,19; 78,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 107,75</t>
+          <t>-41,5; 113,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 36,78</t>
+          <t>-5,02; 35,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 31,04</t>
+          <t>-8,1; 31,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,5; 68,58</t>
+          <t>15,76; 66,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 31,05</t>
+          <t>-5,33; 29,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,2; 38,67</t>
+          <t>1,85; 38,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 70,27</t>
+          <t>-15,41; 70,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 5,97</t>
+          <t>-8,6; 5,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 1,71</t>
+          <t>-11,19; 2,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 11,03</t>
+          <t>-1,57; 11,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 15,94</t>
+          <t>2,5; 16,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 9,81</t>
+          <t>-4,32; 9,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 10,23</t>
+          <t>-1,86; 9,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 8,84</t>
+          <t>-1,2; 8,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 3,76</t>
+          <t>-5,85; 3,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 8,46</t>
+          <t>-0,08; 8,8</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 15,45</t>
+          <t>-18,56; 14,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 4,63</t>
+          <t>-25,01; 7,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 29,09</t>
+          <t>-3,53; 30,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,11; 33,32</t>
+          <t>4,61; 35,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 20,63</t>
+          <t>-7,71; 19,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 21,66</t>
+          <t>-3,45; 20,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 20,19</t>
+          <t>-2,57; 19,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 8,36</t>
+          <t>-11,85; 9,22</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 19,04</t>
+          <t>-0,15; 19,94</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>11,16; 27,88</t>
+          <t>11,59; 26,97</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 12,59</t>
+          <t>-2,19; 13,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 11,77</t>
+          <t>-2,14; 11,96</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 10,72</t>
+          <t>-2,06; 10,99</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 4,2</t>
+          <t>-9,19; 3,77</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 24,13</t>
+          <t>-2,91; 21,84</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,46; 17,41</t>
+          <t>6,11; 16,17</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 5,82</t>
+          <t>-4,33; 5,95</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,1; 22,45</t>
+          <t>0,16; 23,06</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19,71; 58,42</t>
+          <t>20,12; 56,69</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 26,48</t>
+          <t>-3,9; 27,68</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 24,77</t>
+          <t>-3,75; 25,29</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 15,52</t>
+          <t>-2,75; 16,12</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 5,99</t>
+          <t>-12,29; 5,18</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 37,17</t>
+          <t>-3,89; 33,5</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,9; 29,0</t>
+          <t>9,6; 26,9</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 9,58</t>
+          <t>-6,59; 9,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,14; 36,82</t>
+          <t>0,24; 38,36</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,13; 21,22</t>
+          <t>4,7; 21,48</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 12,12</t>
+          <t>-3,29; 12,68</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 12,76</t>
+          <t>-2,33; 13,35</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,76; 15,18</t>
+          <t>3,75; 15,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 7,47</t>
+          <t>-5,61; 7,42</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 8,15</t>
+          <t>-2,15; 8,63</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,02; 15,14</t>
+          <t>6,49; 15,43</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 7,22</t>
+          <t>-2,52; 6,66</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 8,08</t>
+          <t>-0,54; 8,06</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,15; 32,97</t>
+          <t>6,43; 34,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 18,89</t>
+          <t>-4,41; 19,8</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 19,89</t>
+          <t>-3,08; 20,8</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,57; 19,77</t>
+          <t>4,49; 19,74</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 9,66</t>
+          <t>-6,77; 9,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 10,59</t>
+          <t>-2,55; 11,37</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,62; 20,81</t>
+          <t>8,11; 21,2</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 9,77</t>
+          <t>-3,23; 9,0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 11,08</t>
+          <t>-0,68; 10,98</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,68</t>
+          <t>2,64; 6,46</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,16</t>
+          <t>2,02; 6,1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4,45; 13,78</t>
+          <t>3,88; 13,74</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,54</t>
+          <t>2,91; 7,78</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,86</t>
+          <t>0,25; 5,14</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,28; 25,1</t>
+          <t>11,53; 24,7</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,41</t>
+          <t>3,3; 6,48</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,84</t>
+          <t>1,79; 4,91</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>9,57; 19,1</t>
+          <t>9,49; 18,67</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>11,93; 35,01</t>
+          <t>12,67; 34,49</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10,27; 32,93</t>
+          <t>9,85; 32,38</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23,42; 71,63</t>
+          <t>20,0; 71,67</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8,1; 23,37</t>
+          <t>8,22; 23,97</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,5; 15,04</t>
+          <t>0,73; 16,32</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>32,79; 74,1</t>
+          <t>34,13; 75,17</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,51; 24,46</t>
+          <t>11,99; 24,96</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>6,54; 18,65</t>
+          <t>6,39; 18,83</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>35,07; 71,72</t>
+          <t>35,35; 70,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_2-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,31</t>
+          <t>8,53</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,69</t>
+          <t>12,59</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,1</t>
+          <t>10,35</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,79</t>
+          <t>-1,35; 2,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,71</t>
+          <t>-0,91; 3,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 16,7</t>
+          <t>4,01; 14,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 5,87</t>
+          <t>-1,72; 5,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 5,46</t>
+          <t>-1,79; 5,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 18,34</t>
+          <t>6,66; 20,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,49</t>
+          <t>-0,74; 3,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 3,7</t>
+          <t>-0,57; 3,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,93; 14,52</t>
+          <t>6,7; 15,15</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>398,96%</t>
+          <t>365,2%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>149,3%</t>
+          <t>160,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>201,72%</t>
+          <t>206,81%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 217,63</t>
+          <t>-45,25; 168,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 266,4</t>
+          <t>-34,56; 234,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116,97; 1006,43</t>
+          <t>114,42; 977,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 91,2</t>
+          <t>-18,55; 94,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 87,21</t>
+          <t>-20,78; 85,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,67; 299,94</t>
+          <t>73,67; 330,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 85,49</t>
+          <t>-12,77; 83,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 90,18</t>
+          <t>-9,46; 90,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>101,88; 342,89</t>
+          <t>117,13; 345,29</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,88</t>
+          <t>7,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,43</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14,12</t>
+          <t>7,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 5,23</t>
+          <t>0,07; 4,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,98</t>
+          <t>-0,86; 4,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,04</t>
+          <t>3,61; 11,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 0,74</t>
+          <t>-7,21; 0,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 1,14</t>
+          <t>-6,65; 1,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 44,77</t>
+          <t>2,35; 11,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 2,05</t>
+          <t>-2,18; 2,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 2,52</t>
+          <t>-2,51; 2,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 32,9</t>
+          <t>4,45; 10,58</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156,96%</t>
+          <t>163,13%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>124,41%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>153,82%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 159,65</t>
+          <t>0,06; 141,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 120,42</t>
+          <t>-17,25; 127,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,49; 331,52</t>
+          <t>64,53; 311,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,19; 6,1</t>
+          <t>-43,76; 4,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,53; 9,02</t>
+          <t>-38,91; 13,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,24; 349,03</t>
+          <t>13,2; 91,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 24,99</t>
+          <t>-21,42; 26,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,84; 31,19</t>
+          <t>-24,76; 25,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>75,25; 391,54</t>
+          <t>43,56; 129,53</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>4,34</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,83</t>
+          <t>9,78</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,07</t>
+          <t>6,9</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 4,18</t>
+          <t>-2,82; 3,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 3,03</t>
+          <t>-3,39; 3,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 8,96</t>
+          <t>0,51; 8,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 9,18</t>
+          <t>0,38; 9,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 1,77</t>
+          <t>-6,31; 1,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 11,3</t>
+          <t>4,89; 13,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 5,65</t>
+          <t>-0,22; 5,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 1,12</t>
+          <t>-4,05; 1,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 9,26</t>
+          <t>3,88; 9,56</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>48,37%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 53,29</t>
+          <t>-26,02; 48,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,8; 40,76</t>
+          <t>-30,89; 37,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,84; 111,34</t>
+          <t>3,51; 101,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 54,73</t>
+          <t>1,17; 54,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 10,59</t>
+          <t>-29,84; 11,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 67,84</t>
+          <t>23,13; 81,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 43,11</t>
+          <t>-1,38; 43,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 8,71</t>
+          <t>-26,25; 9,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,8; 71,03</t>
+          <t>24,39; 73,94</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>14,47</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,49</t>
+          <t>14,11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,39</t>
+          <t>14,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 5,42</t>
+          <t>-3,59; 5,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 10,57</t>
+          <t>1,23; 10,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 16,94</t>
+          <t>9,56; 19,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 9,56</t>
+          <t>-1,91; 9,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 8,21</t>
+          <t>-3,29; 7,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 17,31</t>
+          <t>8,62; 18,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 6,2</t>
+          <t>-1,42; 6,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 7,88</t>
+          <t>0,73; 8,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 15,43</t>
+          <t>10,59; 17,55</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>64,7%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 40,89</t>
+          <t>-20,4; 42,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,19; 78,53</t>
+          <t>6,65; 83,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,5; 113,88</t>
+          <t>51,8; 152,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 35,0</t>
+          <t>-5,89; 36,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 31,85</t>
+          <t>-10,08; 29,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,76; 66,4</t>
+          <t>26,25; 73,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 29,64</t>
+          <t>-5,93; 29,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 38,2</t>
+          <t>3,0; 40,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 70,94</t>
+          <t>43,21; 86,38</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,22 +1513,22 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>4,78</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-1,09</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>4,28</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4,1</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>4,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 5,65</t>
+          <t>-8,36; 5,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 2,79</t>
+          <t>-12,19; 1,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 11,21</t>
+          <t>-2,24; 10,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,5; 16,62</t>
+          <t>1,82; 16,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 9,31</t>
+          <t>-3,52; 9,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 9,9</t>
+          <t>-0,74; 10,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 8,9</t>
+          <t>-0,9; 8,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 3,98</t>
+          <t>-6,19; 3,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 8,8</t>
+          <t>-0,09; 8,32</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 14,91</t>
+          <t>-18,71; 14,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-25,01; 7,28</t>
+          <t>-26,59; 3,79</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 30,04</t>
+          <t>-4,87; 26,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,61; 35,73</t>
+          <t>3,63; 34,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 19,77</t>
+          <t>-6,87; 20,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 20,27</t>
+          <t>-1,31; 22,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 19,99</t>
+          <t>-2,12; 20,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 9,22</t>
+          <t>-12,57; 8,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 19,94</t>
+          <t>-0,17; 18,84</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,77</t>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8,98</t>
+          <t>1,66</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>11,59; 26,97</t>
+          <t>11,45; 27,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 13,36</t>
+          <t>-3,59; 12,01</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 11,96</t>
+          <t>-2,33; 11,52</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 10,99</t>
+          <t>-2,18; 11,07</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 3,77</t>
+          <t>-9,12; 4,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 21,84</t>
+          <t>-5,87; 5,44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,11; 16,17</t>
+          <t>6,41; 16,44</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 5,95</t>
+          <t>-4,8; 5,62</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,16; 23,06</t>
+          <t>-3,18; 6,06</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>-0,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20,12; 56,69</t>
+          <t>20,36; 60,29</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 27,68</t>
+          <t>-6,27; 24,52</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 25,29</t>
+          <t>-3,79; 24,57</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 16,12</t>
+          <t>-2,71; 16,17</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 5,18</t>
+          <t>-12,52; 6,67</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 33,5</t>
+          <t>-7,77; 7,8</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,6; 26,9</t>
+          <t>9,81; 27,08</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 9,97</t>
+          <t>-7,38; 9,3</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,24; 38,36</t>
+          <t>-4,84; 10,31</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>5,09</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,5</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4,7; 21,48</t>
+          <t>4,69; 20,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 12,68</t>
+          <t>-3,17; 13,09</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 13,35</t>
+          <t>-2,34; 13,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,75; 15,0</t>
+          <t>3,87; 14,84</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 7,42</t>
+          <t>-5,32; 6,9</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 8,63</t>
+          <t>-2,59; 8,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,49; 15,43</t>
+          <t>5,56; 15,07</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 6,66</t>
+          <t>-3,89; 6,93</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 8,06</t>
+          <t>-0,66; 7,6</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>6,43; 34,16</t>
+          <t>6,57; 31,93</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 19,8</t>
+          <t>-4,17; 20,62</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 20,8</t>
+          <t>-3,14; 21,38</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,49; 19,74</t>
+          <t>4,76; 19,61</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 9,57</t>
+          <t>-6,48; 8,9</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 11,37</t>
+          <t>-3,11; 10,69</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,11; 21,2</t>
+          <t>7,27; 20,66</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 9,0</t>
+          <t>-4,85; 9,29</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 10,98</t>
+          <t>-0,82; 10,45</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10,71</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,84</t>
+          <t>12,63</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>13,5</t>
+          <t>12,66</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,46</t>
+          <t>2,24; 6,59</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,1</t>
+          <t>2,04; 6,13</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3,88; 13,74</t>
+          <t>10,31; 14,98</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,78</t>
+          <t>2,85; 7,43</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,14</t>
+          <t>0,1; 4,94</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,53; 24,7</t>
+          <t>10,43; 14,76</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,48</t>
+          <t>3,24; 6,49</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,91</t>
+          <t>1,91; 4,94</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>9,49; 18,67</t>
+          <t>10,98; 14,26</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>12,67; 34,49</t>
+          <t>10,63; 34,53</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>9,85; 32,38</t>
+          <t>9,23; 32,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>20,0; 71,67</t>
+          <t>49,57; 79,72</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8,22; 23,97</t>
+          <t>8,34; 23,05</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,73; 16,32</t>
+          <t>0,22; 15,09</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>34,13; 75,17</t>
+          <t>29,65; 45,36</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,99; 24,96</t>
+          <t>11,78; 24,8</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>6,39; 18,83</t>
+          <t>6,93; 19,13</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>35,35; 70,05</t>
+          <t>40,05; 55,09</t>
         </is>
       </c>
     </row>
